--- a/testcases/generated/自定义厂家/自定义厂家分类图标_20260408.xlsx
+++ b/testcases/generated/自定义厂家/自定义厂家分类图标_20260408.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b67e4dc8a77a56f8/Project/QA/testcases/generated/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b67e4dc8a77a56f8/Project/QA/testcases/generated/自定义厂家/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{EF5DB9B2-2320-4748-80DF-DF8095D1B2C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85A41B1D-2193-B047-B75D-734131DDFAFE}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{EF5DB9B2-2320-4748-80DF-DF8095D1B2C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF32048A-E1F8-7948-8F54-8061B4598203}"/>
   <bookViews>
     <workbookView xWindow="38400" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="81">
   <si>
     <t>序号</t>
   </si>
@@ -161,20 +161,6 @@
     <t>【异常测试】【P1】</t>
   </si>
   <si>
-    <t>【边界测试】【P1】</t>
-  </si>
-  <si>
-    <t>分类图标上传 - 文件大小校验</t>
-  </si>
-  <si>
-    <t>1、点击上传
-2、选择超过限制大小的图片文件</t>
-  </si>
-  <si>
-    <t>1、提示文件大小超出限制
-2、上传失败</t>
-  </si>
-  <si>
     <t>分类图标保存功能 - 成功保存</t>
   </si>
   <si>
@@ -198,10 +184,6 @@
     <t>1、点击重置按钮</t>
   </si>
   <si>
-    <t>1、已选择的图片被清空
-2、恢复到未配置状态</t>
-  </si>
-  <si>
     <t>【功能测试】【P2】</t>
   </si>
   <si>
@@ -239,28 +221,6 @@
     <t>账服</t>
   </si>
   <si>
-    <t>自定义厂家 - 分类图标上传</t>
-  </si>
-  <si>
-    <t>图标保存配置 - 默认兜底逻辑</t>
-  </si>
-  <si>
-    <t>1、某自定义厂家未配置分类图标</t>
-  </si>
-  <si>
-    <t>1、查询该厂家配置信息</t>
-  </si>
-  <si>
-    <t>1、返回配置信息中图标字段为空或 null
-2、标识为使用兜底图标</t>
-  </si>
-  <si>
-    <t>图标保存配置 - 已配置使用配置值</t>
-  </si>
-  <si>
-    <t>1、返回配置信息中包含已上传的图标 URL</t>
-  </si>
-  <si>
     <t>游戏大厅 - 自定义厂家分类展示</t>
   </si>
   <si>
@@ -343,6 +303,11 @@
   </si>
   <si>
     <t>自定义厂家图标上传</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、已选择的图片被清空
+2、恢复到打开弹窗时的图片</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -668,10 +633,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -996,7 +957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" style="3" customWidth="1"/>
@@ -1023,7 +984,7 @@
       </c>
       <c r="H1" s="7">
         <f>H2+H3+H4</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J1" s="9"/>
     </row>
@@ -1032,7 +993,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C2" s="25"/>
       <c r="D2" s="26"/>
@@ -1044,8 +1005,8 @@
         <v>12</v>
       </c>
       <c r="H2" s="13">
-        <f>COUNTIF(H8:H23,G2)</f>
-        <v>0</v>
+        <f>COUNTIF(H8:H20,G2)</f>
+        <v>9</v>
       </c>
       <c r="J2" s="9"/>
     </row>
@@ -1064,7 +1025,7 @@
         <v>15</v>
       </c>
       <c r="H3" s="15">
-        <f>COUNTIF(H8:H23,G3)</f>
+        <f>COUNTIF(H8:H20,G3)</f>
         <v>0</v>
       </c>
       <c r="J3" s="9"/>
@@ -1084,7 +1045,7 @@
         <v>18</v>
       </c>
       <c r="H4" s="18">
-        <f>COUNTIF(H8:H23,G4)</f>
+        <f>COUNTIF(H8:H20,G4)</f>
         <v>0</v>
       </c>
       <c r="J4" s="9"/>
@@ -1148,7 +1109,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>23</v>
@@ -1165,7 +1126,9 @@
       <c r="G8" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H8" s="23"/>
+      <c r="H8" s="23" t="s">
+        <v>12</v>
+      </c>
       <c r="I8" s="3" t="s">
         <v>28</v>
       </c>
@@ -1175,7 +1138,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>23</v>
@@ -1192,7 +1155,9 @@
       <c r="G9" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="23"/>
+      <c r="H9" s="23" t="s">
+        <v>12</v>
+      </c>
       <c r="I9" s="3" t="s">
         <v>28</v>
       </c>
@@ -1202,7 +1167,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>23</v>
@@ -1224,21 +1189,21 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="32">
+    <row r="11" spans="1:10" ht="48">
       <c r="A11" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>34</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>40</v>
@@ -1246,17 +1211,19 @@
       <c r="G11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="H11" s="23"/>
+      <c r="H11" s="23" t="s">
+        <v>12</v>
+      </c>
       <c r="I11" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="48">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="32">
       <c r="A12" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>23</v>
@@ -1271,19 +1238,21 @@
         <v>44</v>
       </c>
       <c r="G12" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="H12" s="23"/>
-      <c r="I12" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="32">
       <c r="A13" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>23</v>
@@ -1300,17 +1269,19 @@
       <c r="G13" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="H13" s="23"/>
+      <c r="H13" s="23" t="s">
+        <v>12</v>
+      </c>
       <c r="I13" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="32">
+    <row r="14" spans="1:10" ht="48">
       <c r="A14" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>23</v>
@@ -1327,251 +1298,178 @@
       <c r="G14" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H14" s="23"/>
+      <c r="H14" s="23" t="s">
+        <v>12</v>
+      </c>
       <c r="I14" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="48">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="32">
       <c r="A15" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>12</v>
+      </c>
       <c r="I15" s="3" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="32">
       <c r="A16" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="F16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>65</v>
       </c>
       <c r="H16" s="23"/>
       <c r="I16" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="16">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="32">
       <c r="A17" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>67</v>
       </c>
       <c r="H17" s="23"/>
       <c r="I17" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="32">
       <c r="A18" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="F18" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H18" s="23"/>
+      <c r="H18" s="23" t="s">
+        <v>12</v>
+      </c>
       <c r="I18" s="3" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="32">
       <c r="A19" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="H19" s="23"/>
+      <c r="H19" s="23" t="s">
+        <v>12</v>
+      </c>
       <c r="I19" s="3" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="32">
       <c r="A20" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="F20" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="G20" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>79</v>
       </c>
       <c r="H20" s="23"/>
       <c r="I20" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="32">
-      <c r="A21" s="3">
-        <v>14</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="H21" s="23"/>
-      <c r="I21" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="32">
-      <c r="A22" s="3">
-        <v>15</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="H22" s="23"/>
-      <c r="I22" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="32">
-      <c r="A23" s="3">
-        <v>16</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="H23" s="23"/>
-      <c r="I23" s="3" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1585,7 +1483,7 @@
     <mergeCell ref="B5:D5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="H8:H23">
+  <conditionalFormatting sqref="H8:H20">
     <cfRule type="cellIs" dxfId="2" priority="1" stopIfTrue="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
@@ -1597,7 +1495,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8:H23" xr:uid="{6D313415-9866-2748-A225-74ED3EBC45DC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8:H20" xr:uid="{6D313415-9866-2748-A225-74ED3EBC45DC}">
       <formula1>$G$2:$G$4</formula1>
     </dataValidation>
   </dataValidations>
